--- a/docs/交通費計算.xlsx
+++ b/docs/交通費計算.xlsx
@@ -290,7 +290,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">3</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -320,7 +320,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">周船寺～天神間は</t>
+      <t xml:space="preserve">最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分）。周船寺～天神間は</t>
     </r>
     <r>
       <rPr>
@@ -1230,7 +1249,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -1587,7 +1606,7 @@
       </c>
       <c r="C10" s="12" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$E$2:$E$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>周船寺→(JR筑肥線・地下鉄空港線 直通)→天神→(徒歩)→天神南→(地下鉄七隈線)→福大前→(徒歩約3分)</v>
+        <v>周船寺→(JR筑肥線・地下鉄空港線 直通)→天神→(徒歩)→天神南→(地下鉄七隈線)→福大前→(徒歩約1分)</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1654,7 +1673,7 @@
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$H$2:$H$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>周船寺～天神間は570円（JR筑肥線270円＋福岡市地下鉄空港線300円、乗換なしの直通、2026年8月時点の検索結果に基づく）まで確認済み。天神～天神南駅間は徒歩連絡のため運賃加算なし。天神南～福大前駅（地下鉄七隈線）の運賃、およびバス利用時の経路・運賃は未確認です。ご利用前にYahoo!路線情報・駅探等の公式経路検索で最終確認のうえ、電車運賃・バス運賃欄（黄色セル）に金額を入力してください。</v>
+        <v>最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約1分）。周船寺～天神間は570円（JR筑肥線270円＋福岡市地下鉄空港線300円、乗換なしの直通、2026年8月時点の検索結果に基づく）まで確認済み。天神～天神南駅間は徒歩連絡のため運賃加算なし。天神南～福大前駅（地下鉄七隈線）の運賃、およびバス利用時の経路・運賃は未確認です。ご利用前にYahoo!路線情報・駅探等の公式経路検索で最終確認のうえ、電車運賃・バス運賃欄（黄色セル）に金額を入力してください。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/交通費計算.xlsx
+++ b/docs/交通費計算.xlsx
@@ -185,7 +185,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">天神→</t>
+      <t xml:space="preserve">博多</t>
     </r>
     <r>
       <rPr>
@@ -204,7 +204,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">徒歩</t>
+      <t xml:space="preserve">同一駅構内で乗換</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地下鉄七隈線</t>
     </r>
     <r>
       <rPr>
@@ -223,7 +242,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">天神南→</t>
+      <t xml:space="preserve">福大前→</t>
     </r>
     <r>
       <rPr>
@@ -242,44 +261,6 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">地下鉄七隈線</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">福大前→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">徒歩約</t>
     </r>
     <r>
@@ -339,7 +320,64 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分）。周船寺～天神間は</t>
+      <t xml:space="preserve">分）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月の七隈線延伸により、空港線との乗換駅は天神南駅から博多駅（同一駅構内での乗換）に変更されました。片道運賃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">870</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円＝周船寺～博多間</t>
     </r>
     <r>
       <rPr>
@@ -415,7 +453,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円、乗換なしの直通、</t>
+      <t xml:space="preserve">円、直通）＋博多～福大前間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（地下鉄七隈線）の合算です（</t>
     </r>
     <r>
       <rPr>
@@ -453,7 +510,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月時点の検索結果に基づく）まで確認済み。天神～天神南駅間は徒歩連絡のため運賃加算なし。天神南～福大前駅（地下鉄七隈線）の運賃、およびバス利用時の経路・運賃は未確認です。ご利用前に</t>
+      <t xml:space="preserve">月時点の検索結果に基づく試算）。ご利用前に一度、</t>
     </r>
     <r>
       <rPr>
@@ -472,7 +529,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">路線情報・駅探等の公式経路検索で最終確認のうえ、電車運賃・バス運賃欄（黄色セル）に金額を入力してください。</t>
+      <t xml:space="preserve">路線情報・駅探等の公式経路検索や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カード実乗車で最終確認をお願いします。</t>
     </r>
   </si>
   <si>
@@ -696,10 +772,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -791,6 +868,13 @@
       <sz val="12"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -943,7 +1027,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -955,7 +1039,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1265,7 +1349,9 @@
       <c r="E2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="5"/>
+      <c r="F2" s="5" t="n">
+        <v>870</v>
+      </c>
       <c r="G2" s="5"/>
       <c r="H2" s="4" t="s">
         <v>12</v>
@@ -1606,7 +1692,7 @@
       </c>
       <c r="C10" s="12" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$E$2:$E$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>周船寺→(JR筑肥線・地下鉄空港線 直通)→天神→(徒歩)→天神南→(地下鉄七隈線)→福大前→(徒歩約1分)</v>
+        <v>周船寺→(JR筑肥線・地下鉄空港線 直通)→博多(同一駅構内で乗換)→(地下鉄七隈線)→福大前→(徒歩約1分)</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1615,7 +1701,7 @@
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$F$2:$F$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),0)</f>
-        <v>0</v>
+        <v>870</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1633,34 +1719,34 @@
       </c>
       <c r="C13" s="12" t="str">
         <f aca="false">IF(C11&gt;0,"電車",IF(C12&gt;0,"バス","要確認（運賃マスタ未入力）"))</f>
-        <v>要確認（運賃マスタ未入力）</v>
+        <v>電車</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="12" t="str">
+      <c r="C14" s="12" t="n">
         <f aca="false">IF(C11&gt;0,C11,IF(C12&gt;0,C12,"要確認"))</f>
-        <v>要確認</v>
+        <v>870</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="12" t="str">
+      <c r="C15" s="12" t="n">
         <f aca="false">IF(ISNUMBER(C14),C14*2,"要確認")</f>
-        <v>要確認</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="14" t="str">
+      <c r="C16" s="14" t="n">
         <f aca="false">IF(ISNUMBER(C15),C15*C7,"要確認")</f>
-        <v>要確認</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1673,7 +1759,7 @@
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$H$2:$H$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約1分）。周船寺～天神間は570円（JR筑肥線270円＋福岡市地下鉄空港線300円、乗換なしの直通、2026年8月時点の検索結果に基づく）まで確認済み。天神～天神南駅間は徒歩連絡のため運賃加算なし。天神南～福大前駅（地下鉄七隈線）の運賃、およびバス利用時の経路・運賃は未確認です。ご利用前にYahoo!路線情報・駅探等の公式経路検索で最終確認のうえ、電車運賃・バス運賃欄（黄色セル）に金額を入力してください。</v>
+        <v>最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約1分）。2023年3月の七隈線延伸により、空港線との乗換駅は天神南駅から博多駅（同一駅構内での乗換）に変更されました。片道運賃870円＝周船寺～博多間570円（JR筑肥線270円＋福岡市地下鉄空港線300円、直通）＋博多～福大前間300円（地下鉄七隈線）の合算です（2026年8月時点の検索結果に基づく試算）。ご利用前に一度、Yahoo!路線情報・駅探等の公式経路検索やICカード実乗車で最終確認をお願いします。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/docs/交通費計算.xlsx
+++ b/docs/交通費計算.xlsx
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -166,7 +166,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">筑肥線・地下鉄空港線 直通</t>
+      <t xml:space="preserve">筑肥線</t>
     </r>
     <r>
       <rPr>
@@ -185,6 +185,44 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">姪浜→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地下鉄空港線 直通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">博多</t>
     </r>
     <r>
@@ -320,7 +358,121 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">分）。</t>
+      <t xml:space="preserve">分）。推奨ルート：周船寺→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">筑肥線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">姪浜→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地下鉄空港線 直通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">博多→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">地下鉄七隈線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福大前（</t>
     </r>
     <r>
       <rPr>
@@ -358,7 +510,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">月の七隈線延伸により、空港線との乗換駅は天神南駅から博多駅（同一駅構内での乗換）に変更されました。片道運賃</t>
+      <t xml:space="preserve">月の七隈線延伸により、乗換駅は天神南駅から博多駅・同一駅構内に変更）。片道運賃は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">650</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円（駅探の運賃検索結果に基づく、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～地下鉄の連絡運賃込みの通し運賃）。※各区間の単独運賃を単純合算すると</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">570</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">300</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円＝</t>
     </r>
     <r>
       <rPr>
@@ -377,7 +605,453 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円＝周船寺～博多間</t>
+      <t xml:space="preserve">円になりますが、これは実際の連絡運賃とは異なり過大な金額になるため使用しないでください。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">650</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月時点の検索結果に基づく数値です。ご利用前に一度、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">路線情報・駅探等の公式経路検索や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">IC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">カード実乗車で最終確認をお願いします。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">福岡徳洲会病院</t>
+  </si>
+  <si>
+    <t xml:space="preserve">南福岡駅→西鉄バス</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">周船寺→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">筑肥線・地下鉄空港線直通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">博多→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹿児島本線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">南福岡→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">西鉄バス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">系統・約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福岡徳洲会病院</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福岡徳洲会病院（春日市須玖北</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4-5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は最寄り駅（南福岡駅・笹原駅）から徒歩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分と遠く、電車のみでは到達できないため、南福岡駅から西鉄バス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">45</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">系統（約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">210</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円）に乗り継ぐ想定です。運賃は未入力です。周船寺～南福岡間は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">筑肥線→地下鉄空港線→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">鹿児島本線という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">社局にまたがる連絡運賃となり、区間ごとの単独運賃（周船寺～博多</t>
     </r>
     <r>
       <rPr>
@@ -396,26 +1070,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">筑肥線</t>
+      <t xml:space="preserve">円＋博多～南福岡</t>
     </r>
     <r>
       <rPr>
@@ -434,83 +1089,7 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円＋福岡市地下鉄空港線</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円、直通）＋博多～福大前間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">300</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円（地下鉄七隈線）の合算です（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月時点の検索結果に基づく試算）。ご利用前に一度、</t>
+      <t xml:space="preserve">円）を単純合算すると実際の連絡運賃より高く出るおそれがあるため、正確な金額はここでは算出していません。ご利用前に</t>
     </r>
     <r>
       <rPr>
@@ -529,26 +1108,26 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">路線情報・駅探等の公式経路検索や</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">カード実乗車で最終確認をお願いします。</t>
+      <t xml:space="preserve">路線情報・駅探等で「周船寺→南福岡」の運賃を確認し、西鉄バス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">210</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円を加えた金額を電車運賃欄に入力してください。</t>
     </r>
   </si>
   <si>
@@ -1333,7 +1912,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="189.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
@@ -1350,48 +1929,58 @@
         <v>11</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>870</v>
+        <v>650</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="n">
+    </row>
+    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5" t="n">
         <v>420</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="6"/>
+      <c r="H4" s="4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
@@ -1631,7 +2220,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -1639,18 +2228,18 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1659,7 +2248,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>9</v>
@@ -1667,7 +2256,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>1</v>
@@ -1688,11 +2277,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C10" s="12" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$E$2:$E$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>周船寺→(JR筑肥線・地下鉄空港線 直通)→博多(同一駅構内で乗換)→(地下鉄七隈線)→福大前→(徒歩約1分)</v>
+        <v>周船寺→(JR筑肥線)→姪浜→(地下鉄空港線 直通)→博多(同一駅構内で乗換)→(地下鉄七隈線)→福大前→(徒歩約1分)</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1701,7 +2290,7 @@
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$F$2:$F$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),0)</f>
-        <v>870</v>
+        <v>650</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1715,7 +2304,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C13" s="12" t="str">
         <f aca="false">IF(C11&gt;0,"電車",IF(C12&gt;0,"バス","要確認（運賃マスタ未入力）"))</f>
@@ -1724,29 +2313,29 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">IF(C11&gt;0,C11,IF(C12&gt;0,C12,"要確認"))</f>
-        <v>870</v>
+        <v>650</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">IF(ISNUMBER(C14),C14*2,"要確認")</f>
-        <v>1740</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C16" s="14" t="n">
         <f aca="false">IF(ISNUMBER(C15),C15*C7,"要確認")</f>
-        <v>1740</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,21 +2344,21 @@
     </row>
     <row r="18" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C18" s="15" t="str">
         <f aca="false">IFERROR(INDEX(運賃マスタ!$H$2:$H$21,MATCH($C$6,運賃マスタ!$C$2:$C$21,0)),"")</f>
-        <v>最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約1分）。2023年3月の七隈線延伸により、空港線との乗換駅は天神南駅から博多駅（同一駅構内での乗換）に変更されました。片道運賃870円＝周船寺～博多間570円（JR筑肥線270円＋福岡市地下鉄空港線300円、直通）＋博多～福大前間300円（地下鉄七隈線）の合算です（2026年8月時点の検索結果に基づく試算）。ご利用前に一度、Yahoo!路線情報・駅探等の公式経路検索やICカード実乗車で最終確認をお願いします。</v>
+        <v>最寄り駅は「福大前」駅（福岡市地下鉄七隈線）です。「福岡大学病院前」という駅名ではないのでご注意ください（福大前駅は福岡大学と福岡大学病院に挟まれた場所にあり、病院までは徒歩約1分）。推奨ルート：周船寺→(JR筑肥線)→姪浜→(地下鉄空港線 直通)→博多→(地下鉄七隈線)→福大前（2023年3月の七隈線延伸により、乗換駅は天神南駅から博多駅・同一駅構内に変更）。片道運賃は650円（駅探の運賃検索結果に基づく、JR～地下鉄の連絡運賃込みの通し運賃）。※各区間の単独運賃を単純合算すると570円＋300円＝870円になりますが、これは実際の連絡運賃とは異なり過大な金額になるため使用しないでください。650円は2026年8月時点の検索結果に基づく数値です。ご利用前に一度、Yahoo!路線情報・駅探等の公式経路検索やICカード実乗車で最終確認をお願いします。</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1777,7 +2366,7 @@
     </row>
     <row r="22" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -1785,7 +2374,7 @@
     </row>
     <row r="23" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
@@ -1793,7 +2382,7 @@
     </row>
     <row r="24" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>

--- a/docs/交通費計算.xlsx
+++ b/docs/交通費計算.xlsx
@@ -707,7 +707,34 @@
     <t xml:space="preserve">福岡徳洲会病院</t>
   </si>
   <si>
-    <t xml:space="preserve">南福岡駅→西鉄バス</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">南福岡駅（徒歩約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -755,17 +782,36 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">博多→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(JR</t>
+      <t xml:space="preserve">博多</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">同一駅構内で乗換</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)→(JR</t>
     </r>
     <r>
       <rPr>
@@ -812,36 +858,17 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">西鉄バス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">系統・約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">徒歩約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
     </r>
     <r>
       <rPr>
@@ -899,159 +926,83 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）は最寄り駅（南福岡駅・笹原駅）から徒歩</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">～</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分と遠く、電車のみでは到達できないため、南福岡駅から西鉄バス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">45</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">系統（約</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">210</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円）に乗り継ぐ想定です。運賃は未入力です。周船寺～南福岡間は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">筑肥線→地下鉄空港線→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">JR</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">鹿児島本線という</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">社局にまたがる連絡運賃となり、区間ごとの単独運賃（周船寺～博多</t>
+      <t xml:space="preserve">）は最寄り駅が南福岡駅・笹原駅（徒歩約</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">分）で、徒歩で到達可能なためバス運賃は加算していません。片道運賃</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">640</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円は、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Yahoo!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">路線情報・駅探を確認したユーザー提供情報に基づく値で、このセッションの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Web</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">検索では独自に裏付けが取れていません（周船寺～博多</t>
     </r>
     <r>
       <rPr>
@@ -1089,45 +1040,45 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">円）を単純合算すると実際の連絡運賃より高く出るおそれがあるため、正確な金額はここでは算出していません。ご利用前に</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Yahoo!</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">路線情報・駅探等で「周船寺→南福岡」の運賃を確認し、西鉄バス</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">210</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">円を加えた金額を電車運賃欄に入力してください。</t>
+      <t xml:space="preserve">円を単純合算すると</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">840</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円になりますが、福岡大学病院の例と同様、連絡運賃はこれより安くなる可能性が高く、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">640</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">円という値は妥当性があります）。ご利用前に一度、公式サイト等で最終確認をお願いします。</t>
     </r>
   </si>
   <si>
@@ -1936,7 +1887,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="149.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
@@ -1952,7 +1903,9 @@
       <c r="E3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5" t="n">
+        <v>640</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="4" t="s">
         <v>16</v>
